--- a/docs/platform/p1-kit/boards/board-04-exam.xlsx
+++ b/docs/platform/p1-kit/boards/board-04-exam.xlsx
@@ -22,33 +22,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t xml:space="preserve">④ 現在地ボード：受験ロードマップ</t>
   </si>
   <si>
-    <t xml:space="preserve">模試・テストの結果が出たら、「模試の記録」シートに教科ごとの偏差値（または点数）を入れてください（保護者の方と一緒に）。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「目安」行は初回の計画書の志望の目安を転記します。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">受験生の本名・学校名は書かないでください。入試日程・制度は必ず学校や教育委員会の公式情報で確認してください。合格を保証するものではありません。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">凡例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄色のセル＝あなたが入力する欄（青字）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白いセル＝自動計算（触らない）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+    <t xml:space="preserve">模試・テストの結果が出たら、「模試の記録」シートの黄色の欄に、教科ごとの偏差値（または点数）を入れてください（保護者の方と一緒に）。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">入れると、教科ごとの現在地・志望の目安との差・受験までの模試</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -58,27 +50,42 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">行目の数字は記入例（架空）です。上書きしてお使いください。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve">回あたりに必要な伸び・次の模試での目標が自動で計算されます。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">入試日程・制度は学校や教育委員会の公式情報で確認してください。合格を保証するものではありません。受験生の本名・学校名は書かないでください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">凡例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄色のセル（青字）＝あなたが入力する欄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">緑のセル＝自動で計算される「現在地」と「これからの予定」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その他の白いセル＝自動計算（触らない）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入っている数字は架空の記入例です。上書きしてお使いください。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">このシートは目安を可視化するもので、結果を保証するものではありません。氏名・口座番号・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve">このシートは、入力した数字から機械的に計算した目安です。結果を保証するものではありません。氏名・口座番号・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -88,11 +95,10 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">・パスワードなどは書かないでください。</t>
+      <t xml:space="preserve">・パスワード・学校名などは書かないでください。</t>
     </r>
   </si>
   <si>
@@ -114,65 +120,59 @@
     <t xml:space="preserve">社会</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
+    <t xml:space="preserve">志望の目安</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">教科の平均</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">回目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">週間の学習時間（時間）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">志望の目安</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
+      <t xml:space="preserve">回目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -183,17 +183,15 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF0000FF"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -204,17 +202,15 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF0000FF"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -225,17 +221,15 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF0000FF"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -246,17 +240,15 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF0000FF"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -267,95 +259,147 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※ 架空の記入例（中学</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年・高校受験）です。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">現在地ボード：受験</t>
-  </si>
-  <si>
-    <t xml:space="preserve">教科</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最新</t>
-  </si>
-  <si>
-    <t xml:space="preserve">差</t>
-  </si>
-  <si>
-    <t xml:space="preserve">優先度</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve">回目</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">受験までに受ける模試の回数（全部で）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">※ 差が−</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve">※ 架空の記入例（中学</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">以下を「最優先」、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve">年・高校受験）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">現在地ボード：受験</t>
+  </si>
+  <si>
+    <t xml:space="preserve">受けた模試の回数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">受験までの残りの模試の回数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">教科</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在地</t>
+  </si>
+  <si>
+    <t xml:space="preserve">差</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">未満を「強化」として表示する目安です（初回の計画書の方針を優先してください）。</t>
-    </r>
+      <t xml:space="preserve">回目からの平均の伸び（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回あたり）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目安に届くために必要な伸び（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回あたり）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">次の模試の目標</t>
+  </si>
+  <si>
+    <t xml:space="preserve">今のペースで届く見込み</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 機械的な計算による目安です。時間配分の見直しは、初回の計画書の方針（または模試後の見直し）を優先してください。</t>
   </si>
 </sst>
 </file>
@@ -364,11 +408,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0"/>
-    <numFmt numFmtId="167" formatCode="0;\-0;0"/>
+    <numFmt numFmtId="165" formatCode="0"/>
+    <numFmt numFmtId="166" formatCode="0;\-0;0"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,9 +443,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -417,7 +466,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -428,31 +477,6 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -468,7 +492,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -478,13 +502,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFDDE6F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDE6F5"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -537,7 +567,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -550,51 +580,63 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -626,7 +668,7 @@
       <rgbColor rgb="FFBBBBBB"/>
       <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFBE4B48"/>
       <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFDDE6F5"/>
       <rgbColor rgb="FF660066"/>
@@ -643,19 +685,19 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFE2F0D9"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF4A7EBB"/>
+      <rgbColor rgb="FF46AAC4"/>
+      <rgbColor rgb="FF98B855"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF4A7EBB"/>
+      <rgbColor rgb="FF7D5FA0"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
@@ -696,7 +738,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>5教科の平均の推移</a:t>
+              <a:t>教科別の推移</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -719,11 +761,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>模試の記録!G1</c:f>
+              <c:f>模試の記録!B1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>5教科の平均</c:v>
+                  <c:v>英語</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -769,9 +811,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>模試の記録!$A$2:$A$7</c:f>
+              <c:f>模試の記録!$A$2:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>志望の目安</c:v>
                 </c:pt>
@@ -789,24 +831,465 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>5回目</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6回目</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7回目</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8回目</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>模試の記録!$G$2:$G$7</c:f>
+              <c:f>模試の記録!$B$2:$B$10</c:f>
               <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>59</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>模試の記録!C1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>数学</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>模試の記録!$A$2:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>志望の目安</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1回目</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2回目</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3回目</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4回目</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5回目</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6回目</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7回目</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8回目</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>模試の記録!$C$2:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>52</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>模試の記録!D1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>国語</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>模試の記録!$A$2:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>志望の目安</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1回目</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2回目</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3回目</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4回目</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5回目</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6回目</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7回目</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8回目</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>模試の記録!$D$2:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>56</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>模試の記録!E1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>理科</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7d5fa0"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="7d5fa0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>模試の記録!$A$2:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>志望の目安</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1回目</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2回目</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3回目</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4回目</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5回目</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6回目</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7回目</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8回目</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>模試の記録!$E$2:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>54</c:v>
                 </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>模試の記録!F1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>社会</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="46aac4"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="46aac4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>模試の記録!$A$2:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>志望の目安</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1回目</c:v>
+                </c:pt>
                 <c:pt idx="2">
-                  <c:v>55.2</c:v>
+                  <c:v>2回目</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3回目</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4回目</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5回目</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6回目</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7回目</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8回目</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>模試の記録!$F$2:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -821,11 +1304,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="37041727"/>
-        <c:axId val="1439320"/>
+        <c:axId val="94801511"/>
+        <c:axId val="87016720"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="37041727"/>
+        <c:axId val="94801511"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -857,7 +1340,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1439320"/>
+        <c:crossAx val="87016720"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -865,7 +1348,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1439320"/>
+        <c:axId val="87016720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -881,7 +1364,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -907,7 +1390,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37041727"/>
+        <c:crossAx val="94801511"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -943,7 +1426,7 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
+    <c:dispBlanksAs val="gap"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -963,16 +1446,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>159840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>364680</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>128160</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>714960</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>160920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -980,8 +1463,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4840560" y="380880"/>
-        <a:ext cx="6479640" cy="2879640"/>
+        <a:off x="0" y="2685960"/>
+        <a:ext cx="7199640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1174,10 +1657,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1190,7 +1673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1211,18 +1694,23 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1241,44 +1729,36 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="7" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>17</v>
       </c>
       <c r="B2" s="8" t="n">
         <v>60</v>
@@ -1295,14 +1775,10 @@
       <c r="F2" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="G2" s="9" t="n">
-        <f aca="false">IF(COUNT(B2:F2)=0,"",AVERAGE(B2:F2))</f>
-        <v>60</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
-        <v>18</v>
+      <c r="A3" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="B3" s="8" t="n">
         <v>58</v>
@@ -1319,17 +1795,10 @@
       <c r="F3" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="G3" s="9" t="n">
-        <f aca="false">IF(COUNT(B3:F3)=0,"",AVERAGE(B3:F3))</f>
-        <v>54</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>10</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>19</v>
+      <c r="A4" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>59</v>
@@ -1346,62 +1815,78 @@
       <c r="F4" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="G4" s="9" t="n">
-        <f aca="false">IF(COUNT(B4:F4)=0,"",AVERAGE(B4:F4))</f>
-        <v>55.2</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>12</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>20</v>
+      <c r="A5" s="9" t="s">
+        <v>19</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
-      <c r="G5" s="9" t="str">
-        <f aca="false">IF(COUNT(B5:F5)=0,"",AVERAGE(B5:F5))</f>
-        <v/>
-      </c>
-      <c r="H5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>21</v>
+      <c r="A6" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
-      <c r="G6" s="9" t="str">
-        <f aca="false">IF(COUNT(B6:F6)=0,"",AVERAGE(B6:F6))</f>
-        <v/>
-      </c>
-      <c r="H6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>22</v>
+      <c r="A7" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
-      <c r="G7" s="9" t="str">
-        <f aca="false">IF(COUNT(B7:F7)=0,"",AVERAGE(B7:F7))</f>
-        <v/>
-      </c>
-      <c r="H7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="9" t="s">
         <v>23</v>
+      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1420,142 +1905,235 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="11" t="n">
+        <f aca="false">MAX(COUNT(模試の記録!B3:B10),COUNT(模試の記録!C3:C10),COUNT(模試の記録!D3:D10),COUNT(模試の記録!E3:E10),COUNT(模試の記録!F3:F10))</f>
+        <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="12" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!B3:B7&lt;&gt;""),模試の記録!B3:B7),"")</f>
+      <c r="A3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="11" t="n">
+        <f aca="false">MAX(模試の記録!B12-B2,0)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!B3:B10&lt;&gt;""),模試の記録!B3:B10),"")</f>
         <v>59</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C6" s="11" t="n">
         <f aca="false">模試の記録!B2</f>
         <v>60</v>
       </c>
-      <c r="D4" s="13" t="n">
-        <f aca="false">IFERROR(B4-C4,"")</f>
+      <c r="D6" s="14" t="n">
+        <f aca="false">IFERROR(B6-C6,"")</f>
         <v>-1</v>
       </c>
-      <c r="E4" s="14" t="str">
-        <f aca="false">IFERROR(IF(D4&lt;=-8,"最優先",IF(D4&lt;0,"強化","維持")),"")</f>
-        <v>強化</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="12" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!C3:C7&lt;&gt;""),模試の記録!C3:C7),"")</f>
+      <c r="E6" s="15" t="n">
+        <f aca="false">IFERROR(IF(COUNT(模試の記録!B3:B10)&lt;2,"",(B6-模試の記録!B3)/(COUNT(模試の記録!B3:B10)-1)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <f aca="false">IFERROR(IF(D6&gt;=0,0,IF($B$3=0,"",-D6/$B$3)),"")</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <f aca="false">IFERROR(IF(D6&gt;=0,B6,ROUND(B6+F6,0)),"")</f>
+        <v>59</v>
+      </c>
+      <c r="H6" s="17" t="str">
+        <f aca="false">IFERROR(IF(D6&gt;=0,"目安に到達",IF(E6="","2回以上の記録で表示",IF(E6&gt;=F6,"届く見込み","今のペースでは届かない（配分の見直し）"))),"")</f>
+        <v>届く見込み</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!C3:C10&lt;&gt;""),模試の記録!C3:C10),"")</f>
         <v>52</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C7" s="11" t="n">
         <f aca="false">模試の記録!C2</f>
         <v>60</v>
       </c>
-      <c r="D5" s="13" t="n">
-        <f aca="false">IFERROR(B5-C5,"")</f>
+      <c r="D7" s="14" t="n">
+        <f aca="false">IFERROR(B7-C7,"")</f>
         <v>-8</v>
       </c>
-      <c r="E5" s="14" t="str">
-        <f aca="false">IFERROR(IF(D5&lt;=-8,"最優先",IF(D5&lt;0,"強化","維持")),"")</f>
-        <v>最優先</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="12" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!D3:D7&lt;&gt;""),模試の記録!D3:D7),"")</f>
+      <c r="E7" s="15" t="n">
+        <f aca="false">IFERROR(IF(COUNT(模試の記録!C3:C10)&lt;2,"",(B7-模試の記録!C3)/(COUNT(模試の記録!C3:C10)-1)),"")</f>
+        <v>3</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <f aca="false">IFERROR(IF(D7&gt;=0,0,IF($B$3=0,"",-D7/$B$3)),"")</f>
+        <v>1.33333333333333</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <f aca="false">IFERROR(IF(D7&gt;=0,B7,ROUND(B7+F7,0)),"")</f>
+        <v>53</v>
+      </c>
+      <c r="H7" s="17" t="str">
+        <f aca="false">IFERROR(IF(D7&gt;=0,"目安に到達",IF(E7="","2回以上の記録で表示",IF(E7&gt;=F7,"届く見込み","今のペースでは届かない（配分の見直し）"))),"")</f>
+        <v>届く見込み</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="13" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!D3:D10&lt;&gt;""),模試の記録!D3:D10),"")</f>
         <v>56</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C8" s="11" t="n">
         <f aca="false">模試の記録!D2</f>
         <v>60</v>
       </c>
-      <c r="D6" s="13" t="n">
-        <f aca="false">IFERROR(B6-C6,"")</f>
+      <c r="D8" s="14" t="n">
+        <f aca="false">IFERROR(B8-C8,"")</f>
         <v>-4</v>
       </c>
-      <c r="E6" s="14" t="str">
-        <f aca="false">IFERROR(IF(D6&lt;=-8,"最優先",IF(D6&lt;0,"強化","維持")),"")</f>
-        <v>強化</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="12" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!E3:E7&lt;&gt;""),模試の記録!E3:E7),"")</f>
+      <c r="E8" s="15" t="n">
+        <f aca="false">IFERROR(IF(COUNT(模試の記録!D3:D10)&lt;2,"",(B8-模試の記録!D3)/(COUNT(模試の記録!D3:D10)-1)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <f aca="false">IFERROR(IF(D8&gt;=0,0,IF($B$3=0,"",-D8/$B$3)),"")</f>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <f aca="false">IFERROR(IF(D8&gt;=0,B8,ROUND(B8+F8,0)),"")</f>
+        <v>57</v>
+      </c>
+      <c r="H8" s="17" t="str">
+        <f aca="false">IFERROR(IF(D8&gt;=0,"目安に到達",IF(E8="","2回以上の記録で表示",IF(E8&gt;=F8,"届く見込み","今のペースでは届かない（配分の見直し）"))),"")</f>
+        <v>今のペースでは届かない（配分の見直し）</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="13" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!E3:E10&lt;&gt;""),模試の記録!E3:E10),"")</f>
         <v>54</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C9" s="11" t="n">
         <f aca="false">模試の記録!E2</f>
         <v>60</v>
       </c>
-      <c r="D7" s="13" t="n">
-        <f aca="false">IFERROR(B7-C7,"")</f>
+      <c r="D9" s="14" t="n">
+        <f aca="false">IFERROR(B9-C9,"")</f>
         <v>-6</v>
       </c>
-      <c r="E7" s="14" t="str">
-        <f aca="false">IFERROR(IF(D7&lt;=-8,"最優先",IF(D7&lt;0,"強化","維持")),"")</f>
-        <v>強化</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="12" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!F3:F7&lt;&gt;""),模試の記録!F3:F7),"")</f>
+      <c r="E9" s="15" t="n">
+        <f aca="false">IFERROR(IF(COUNT(模試の記録!E3:E10)&lt;2,"",(B9-模試の記録!E3)/(COUNT(模試の記録!E3:E10)-1)),"")</f>
+        <v>2</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <f aca="false">IFERROR(IF(D9&gt;=0,0,IF($B$3=0,"",-D9/$B$3)),"")</f>
+        <v>1</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <f aca="false">IFERROR(IF(D9&gt;=0,B9,ROUND(B9+F9,0)),"")</f>
         <v>55</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="H9" s="17" t="str">
+        <f aca="false">IFERROR(IF(D9&gt;=0,"目安に到達",IF(E9="","2回以上の記録で表示",IF(E9&gt;=F9,"届く見込み","今のペースでは届かない（配分の見直し）"))),"")</f>
+        <v>届く見込み</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="13" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!F3:F10&lt;&gt;""),模試の記録!F3:F10),"")</f>
+        <v>55</v>
+      </c>
+      <c r="C10" s="11" t="n">
         <f aca="false">模試の記録!F2</f>
         <v>60</v>
       </c>
-      <c r="D8" s="13" t="n">
-        <f aca="false">IFERROR(B8-C8,"")</f>
+      <c r="D10" s="14" t="n">
+        <f aca="false">IFERROR(B10-C10,"")</f>
         <v>-5</v>
       </c>
-      <c r="E8" s="14" t="str">
-        <f aca="false">IFERROR(IF(D8&lt;=-8,"最優先",IF(D8&lt;0,"強化","維持")),"")</f>
-        <v>強化</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>29</v>
+      <c r="E10" s="15" t="n">
+        <f aca="false">IFERROR(IF(COUNT(模試の記録!F3:F10)&lt;2,"",(B10-模試の記録!F3)/(COUNT(模試の記録!F3:F10)-1)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <f aca="false">IFERROR(IF(D10&gt;=0,0,IF($B$3=0,"",-D10/$B$3)),"")</f>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <f aca="false">IFERROR(IF(D10&gt;=0,B10,ROUND(B10+F10,0)),"")</f>
+        <v>56</v>
+      </c>
+      <c r="H10" s="17" t="str">
+        <f aca="false">IFERROR(IF(D10&gt;=0,"目安に到達",IF(E10="","2回以上の記録で表示",IF(E10&gt;=F10,"届く見込み","今のペースでは届かない（配分の見直し）"))),"")</f>
+        <v>今のペースでは届かない（配分の見直し）</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/docs/platform/p1-kit/boards/board-04-exam.xlsx
+++ b/docs/platform/p1-kit/boards/board-04-exam.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
   <si>
     <t xml:space="preserve">④ 現在地ボード：受験ロードマップ</t>
   </si>
@@ -120,6 +120,9 @@
     <t xml:space="preserve">社会</t>
   </si>
   <si>
+    <t xml:space="preserve">模試の名前（会社・シリーズ）</t>
+  </si>
+  <si>
     <t xml:space="preserve">志望の目安</t>
   </si>
   <si>
@@ -142,6 +145,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">（例）◯◯模試</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -359,18 +365,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">回あたり）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目安に届くために必要な伸び（</t>
+      <t xml:space="preserve">回あたり・</t>
     </r>
     <r>
       <rPr>
@@ -380,7 +375,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">3</t>
     </r>
     <r>
       <rPr>
@@ -389,17 +384,50 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">回以上で表示）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目安に届くために必要な伸び（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">回あたり）</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">次の模試の目標</t>
-  </si>
-  <si>
-    <t xml:space="preserve">今のペースで届く見込み</t>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 機械的な計算による目安です。時間配分の見直しは、初回の計画書の方針（または模試後の見直し）を優先してください。</t>
+    <t xml:space="preserve">次の模試の目標（参考）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">今のペースの場合（参考計算）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 見込みと次の模試の目標は、過去の数値を直線で延ばした参考計算で、学力や合格の可能性の予測ではありません。時間配分の見直しは、初回の計画書の方針（または模試後の見直し）を優先してください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 偏差値は、模試の実施会社・受験者層・問題の難しさで変わります。できるだけ同じ会社・同じシリーズの模試の結果を記録してください。違う模試の偏差値は、単純な伸びとして比べられません。</t>
   </si>
 </sst>
 </file>
@@ -567,7 +595,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -605,6 +633,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1304,11 +1336,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="94801511"/>
-        <c:axId val="87016720"/>
+        <c:axId val="46626334"/>
+        <c:axId val="66873715"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="94801511"/>
+        <c:axId val="46626334"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1340,7 +1372,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87016720"/>
+        <c:crossAx val="66873715"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1348,7 +1380,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="87016720"/>
+        <c:axId val="66873715"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1390,7 +1422,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94801511"/>
+        <c:crossAx val="46626334"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1448,13 +1480,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>159840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>714960</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>160920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -1463,7 +1495,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="2685960"/>
+        <a:off x="0" y="2876400"/>
         <a:ext cx="7199640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1729,7 +1761,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1755,10 +1787,13 @@
       <c r="F1" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="G1" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="8" t="n">
         <v>60</v>
@@ -1778,7 +1813,7 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8" t="n">
         <v>58</v>
@@ -1795,10 +1830,13 @@
       <c r="F3" s="8" t="n">
         <v>55</v>
       </c>
+      <c r="G3" s="7" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>59</v>
@@ -1815,70 +1853,79 @@
       <c r="F4" s="8" t="n">
         <v>55</v>
       </c>
+      <c r="G4" s="7" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
+      <c r="G5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
+      <c r="G6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
+      <c r="G7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
+      <c r="G8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>25</v>
+      <c r="A12" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>8</v>
@@ -1886,10 +1933,16 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:F10 G5:G10 B12" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1905,7 +1958,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -1919,221 +1972,226 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="11" t="n">
+      <c r="A2" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="12" t="n">
         <f aca="false">MAX(COUNT(模試の記録!B3:B10),COUNT(模試の記録!C3:C10),COUNT(模試の記録!D3:D10),COUNT(模試の記録!E3:E10),COUNT(模試の記録!F3:F10))</f>
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="11" t="n">
+      <c r="A3" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="12" t="n">
         <f aca="false">MAX(模試の記録!B12-B2,0)</f>
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>35</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="14" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!B3:B10&lt;&gt;""),模試の記録!B3:B10),"")</f>
         <v>59</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <f aca="false">模試の記録!B2</f>
         <v>60</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <f aca="false">IFERROR(B6-C6,"")</f>
         <v>-1</v>
       </c>
-      <c r="E6" s="15" t="n">
-        <f aca="false">IFERROR(IF(COUNT(模試の記録!B3:B10)&lt;2,"",(B6-模試の記録!B3)/(COUNT(模試の記録!B3:B10)-1)),"")</f>
-        <v>1</v>
-      </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="16" t="str">
+        <f aca="false">IFERROR(IF(COUNT(模試の記録!B3:B10)&lt;3,"",(B6-模試の記録!B3)/(COUNT(模試の記録!B3:B10)-1)),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="17" t="n">
         <f aca="false">IFERROR(IF(D6&gt;=0,0,IF($B$3=0,"",-D6/$B$3)),"")</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="14" t="n">
         <f aca="false">IFERROR(IF(D6&gt;=0,B6,ROUND(B6+F6,0)),"")</f>
         <v>59</v>
       </c>
-      <c r="H6" s="17" t="str">
-        <f aca="false">IFERROR(IF(D6&gt;=0,"目安に到達",IF(E6="","2回以上の記録で表示",IF(E6&gt;=F6,"届く見込み","今のペースでは届かない（配分の見直し）"))),"")</f>
-        <v>届く見込み</v>
+      <c r="H6" s="18" t="str">
+        <f aca="false">IFERROR(IF(B6="","",IF(D6&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E6="","予測データ不足（3回以上で表示）",IF(E6&gt;=F6,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
+        <v>予測データ不足（3回以上で表示）</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!C3:C10&lt;&gt;""),模試の記録!C3:C10),"")</f>
         <v>52</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <f aca="false">模試の記録!C2</f>
         <v>60</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <f aca="false">IFERROR(B7-C7,"")</f>
         <v>-8</v>
       </c>
-      <c r="E7" s="15" t="n">
-        <f aca="false">IFERROR(IF(COUNT(模試の記録!C3:C10)&lt;2,"",(B7-模試の記録!C3)/(COUNT(模試の記録!C3:C10)-1)),"")</f>
-        <v>3</v>
-      </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="16" t="str">
+        <f aca="false">IFERROR(IF(COUNT(模試の記録!C3:C10)&lt;3,"",(B7-模試の記録!C3)/(COUNT(模試の記録!C3:C10)-1)),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="17" t="n">
         <f aca="false">IFERROR(IF(D7&gt;=0,0,IF($B$3=0,"",-D7/$B$3)),"")</f>
         <v>1.33333333333333</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="14" t="n">
         <f aca="false">IFERROR(IF(D7&gt;=0,B7,ROUND(B7+F7,0)),"")</f>
         <v>53</v>
       </c>
-      <c r="H7" s="17" t="str">
-        <f aca="false">IFERROR(IF(D7&gt;=0,"目安に到達",IF(E7="","2回以上の記録で表示",IF(E7&gt;=F7,"届く見込み","今のペースでは届かない（配分の見直し）"))),"")</f>
-        <v>届く見込み</v>
+      <c r="H7" s="18" t="str">
+        <f aca="false">IFERROR(IF(B7="","",IF(D7&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E7="","予測データ不足（3回以上で表示）",IF(E7&gt;=F7,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
+        <v>予測データ不足（3回以上で表示）</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!D3:D10&lt;&gt;""),模試の記録!D3:D10),"")</f>
         <v>56</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <f aca="false">模試の記録!D2</f>
         <v>60</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <f aca="false">IFERROR(B8-C8,"")</f>
         <v>-4</v>
       </c>
-      <c r="E8" s="15" t="n">
-        <f aca="false">IFERROR(IF(COUNT(模試の記録!D3:D10)&lt;2,"",(B8-模試の記録!D3)/(COUNT(模試の記録!D3:D10)-1)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="16" t="str">
+        <f aca="false">IFERROR(IF(COUNT(模試の記録!D3:D10)&lt;3,"",(B8-模試の記録!D3)/(COUNT(模試の記録!D3:D10)-1)),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="17" t="n">
         <f aca="false">IFERROR(IF(D8&gt;=0,0,IF($B$3=0,"",-D8/$B$3)),"")</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="14" t="n">
         <f aca="false">IFERROR(IF(D8&gt;=0,B8,ROUND(B8+F8,0)),"")</f>
         <v>57</v>
       </c>
-      <c r="H8" s="17" t="str">
-        <f aca="false">IFERROR(IF(D8&gt;=0,"目安に到達",IF(E8="","2回以上の記録で表示",IF(E8&gt;=F8,"届く見込み","今のペースでは届かない（配分の見直し）"))),"")</f>
-        <v>今のペースでは届かない（配分の見直し）</v>
+      <c r="H8" s="18" t="str">
+        <f aca="false">IFERROR(IF(B8="","",IF(D8&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E8="","予測データ不足（3回以上で表示）",IF(E8&gt;=F8,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
+        <v>予測データ不足（3回以上で表示）</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!E3:E10&lt;&gt;""),模試の記録!E3:E10),"")</f>
         <v>54</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <f aca="false">模試の記録!E2</f>
         <v>60</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <f aca="false">IFERROR(B9-C9,"")</f>
         <v>-6</v>
       </c>
-      <c r="E9" s="15" t="n">
-        <f aca="false">IFERROR(IF(COUNT(模試の記録!E3:E10)&lt;2,"",(B9-模試の記録!E3)/(COUNT(模試の記録!E3:E10)-1)),"")</f>
-        <v>2</v>
-      </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="16" t="str">
+        <f aca="false">IFERROR(IF(COUNT(模試の記録!E3:E10)&lt;3,"",(B9-模試の記録!E3)/(COUNT(模試の記録!E3:E10)-1)),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="17" t="n">
         <f aca="false">IFERROR(IF(D9&gt;=0,0,IF($B$3=0,"",-D9/$B$3)),"")</f>
         <v>1</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="14" t="n">
         <f aca="false">IFERROR(IF(D9&gt;=0,B9,ROUND(B9+F9,0)),"")</f>
         <v>55</v>
       </c>
-      <c r="H9" s="17" t="str">
-        <f aca="false">IFERROR(IF(D9&gt;=0,"目安に到達",IF(E9="","2回以上の記録で表示",IF(E9&gt;=F9,"届く見込み","今のペースでは届かない（配分の見直し）"))),"")</f>
-        <v>届く見込み</v>
+      <c r="H9" s="18" t="str">
+        <f aca="false">IFERROR(IF(B9="","",IF(D9&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E9="","予測データ不足（3回以上で表示）",IF(E9&gt;=F9,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
+        <v>予測データ不足（3回以上で表示）</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="14" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!F3:F10&lt;&gt;""),模試の記録!F3:F10),"")</f>
         <v>55</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <f aca="false">模試の記録!F2</f>
         <v>60</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <f aca="false">IFERROR(B10-C10,"")</f>
         <v>-5</v>
       </c>
-      <c r="E10" s="15" t="n">
-        <f aca="false">IFERROR(IF(COUNT(模試の記録!F3:F10)&lt;2,"",(B10-模試の記録!F3)/(COUNT(模試の記録!F3:F10)-1)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="16" t="str">
+        <f aca="false">IFERROR(IF(COUNT(模試の記録!F3:F10)&lt;3,"",(B10-模試の記録!F3)/(COUNT(模試の記録!F3:F10)-1)),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="17" t="n">
         <f aca="false">IFERROR(IF(D10&gt;=0,0,IF($B$3=0,"",-D10/$B$3)),"")</f>
         <v>0.833333333333333</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="14" t="n">
         <f aca="false">IFERROR(IF(D10&gt;=0,B10,ROUND(B10+F10,0)),"")</f>
         <v>56</v>
       </c>
-      <c r="H10" s="17" t="str">
-        <f aca="false">IFERROR(IF(D10&gt;=0,"目安に到達",IF(E10="","2回以上の記録で表示",IF(E10&gt;=F10,"届く見込み","今のペースでは届かない（配分の見直し）"))),"")</f>
-        <v>今のペースでは届かない（配分の見直し）</v>
+      <c r="H10" s="18" t="str">
+        <f aca="false">IFERROR(IF(B10="","",IF(D10&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E10="","予測データ不足（3回以上で表示）",IF(E10&gt;=F10,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
+        <v>予測データ不足（3回以上で表示）</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/docs/platform/p1-kit/boards/board-04-exam.xlsx
+++ b/docs/platform/p1-kit/boards/board-04-exam.xlsx
@@ -8,9 +8,10 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="使い方" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="模試の記録" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="ボード" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="スマホ" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="使い方" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="模試の記録" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="ボード" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,12 +23,227 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="54">
+  <si>
+    <t xml:space="preserve">④ スマホで見る：受験</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 現在地（最新の模試）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">英語</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数学</t>
+  </si>
+  <si>
+    <t xml:space="preserve">国語</t>
+  </si>
+  <si>
+    <t xml:space="preserve">理科</t>
+  </si>
+  <si>
+    <t xml:space="preserve">社会</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 次の模試の目標（参考）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">見込みと目標は過去の数値を直線で延ばした参考計算で、合格の可能性の予測ではありません。できるだけ同じ会社・同じシリーズの模試で比べてください。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">受験までの模試の回数（全部）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 数字を入れる（模試ごと・偏差値または点数）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">回</t>
+  </si>
+  <si>
+    <t xml:space="preserve">英</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">国</t>
+  </si>
+  <si>
+    <t xml:space="preserve">理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">社</t>
+  </si>
+  <si>
+    <t xml:space="preserve">志望の目安</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回目</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 模試の名前（会社・シリーズ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（例）◯◯模試</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 教科別の推移</t>
+  </si>
   <si>
     <t xml:space="preserve">④ 現在地ボード：受験ロードマップ</t>
   </si>
   <si>
-    <t xml:space="preserve">模試・テストの結果が出たら、「模試の記録」シートの黄色の欄に、教科ごとの偏差値（または点数）を入れてください（保護者の方と一緒に）。</t>
+    <t xml:space="preserve">模試・テストの結果が出たら、「スマホ」シートの下にある入力欄に、教科ごとの偏差値（または点数）を入れてください（保護者の方と一緒に）。</t>
   </si>
   <si>
     <r>
@@ -102,183 +318,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">回</t>
-  </si>
-  <si>
-    <t xml:space="preserve">英語</t>
-  </si>
-  <si>
-    <t xml:space="preserve">数学</t>
-  </si>
-  <si>
-    <t xml:space="preserve">国語</t>
-  </si>
-  <si>
-    <t xml:space="preserve">理科</t>
-  </si>
-  <si>
-    <t xml:space="preserve">社会</t>
-  </si>
-  <si>
     <t xml:space="preserve">模試の名前（会社・シリーズ）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">志望の目安</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回目</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">（例）◯◯模試</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回目</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">受験までに受ける模試の回数（全部で）</t>
@@ -440,7 +480,7 @@
     <numFmt numFmtId="166" formatCode="0;\-0;0"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,7 +505,13 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
+      <sz val="13"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
@@ -483,12 +529,12 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
@@ -500,11 +546,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="11"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <color rgb="FF0000FF"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -519,6 +564,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -529,14 +580,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFE2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFDDE6F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2F0D9"/>
-        <bgColor rgb="FFDDE6F5"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -546,7 +597,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -561,6 +612,19 @@
       <right style="thin">
         <color rgb="FFBBBBBB"/>
       </right>
+      <top style="thin">
+        <color rgb="FFBBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFBBBBBB"/>
+      </left>
+      <right/>
       <top style="thin">
         <color rgb="FFBBBBBB"/>
       </top>
@@ -595,40 +659,68 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -636,39 +728,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -793,7 +881,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>模試の記録!B1</c:f>
+              <c:f>"英語"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -843,34 +931,31 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>模試の記録!$A$2:$A$10</c:f>
+              <c:f>スマホ!$A$22:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>志望の目安</c:v>
+                  <c:v>1回目</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1回目</c:v>
+                  <c:v>2回目</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2回目</c:v>
+                  <c:v>3回目</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3回目</c:v>
+                  <c:v>4回目</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4回目</c:v>
+                  <c:v>5回目</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5回目</c:v>
+                  <c:v>6回目</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6回目</c:v>
+                  <c:v>7回目</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7回目</c:v>
-                </c:pt>
-                <c:pt idx="8">
                   <c:v>8回目</c:v>
                 </c:pt>
               </c:strCache>
@@ -878,30 +963,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>模試の記録!$B$2:$B$10</c:f>
+              <c:f>スマホ!$B$22:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>60</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>58</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>59</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>模試の記録!C1</c:f>
+              <c:f>"数学"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -951,34 +1033,31 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>模試の記録!$A$2:$A$10</c:f>
+              <c:f>スマホ!$A$22:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>志望の目安</c:v>
+                  <c:v>1回目</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1回目</c:v>
+                  <c:v>2回目</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2回目</c:v>
+                  <c:v>3回目</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3回目</c:v>
+                  <c:v>4回目</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4回目</c:v>
+                  <c:v>5回目</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5回目</c:v>
+                  <c:v>6回目</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6回目</c:v>
+                  <c:v>7回目</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7回目</c:v>
-                </c:pt>
-                <c:pt idx="8">
                   <c:v>8回目</c:v>
                 </c:pt>
               </c:strCache>
@@ -986,30 +1065,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>模試の記録!$C$2:$C$10</c:f>
+              <c:f>スマホ!$C$22:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>60</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>49</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>52</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>模試の記録!D1</c:f>
+              <c:f>"国語"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1059,34 +1135,31 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>模試の記録!$A$2:$A$10</c:f>
+              <c:f>スマホ!$A$22:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>志望の目安</c:v>
+                  <c:v>1回目</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1回目</c:v>
+                  <c:v>2回目</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2回目</c:v>
+                  <c:v>3回目</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3回目</c:v>
+                  <c:v>4回目</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4回目</c:v>
+                  <c:v>5回目</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5回目</c:v>
+                  <c:v>6回目</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6回目</c:v>
+                  <c:v>7回目</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7回目</c:v>
-                </c:pt>
-                <c:pt idx="8">
                   <c:v>8回目</c:v>
                 </c:pt>
               </c:strCache>
@@ -1094,30 +1167,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>模試の記録!$D$2:$D$10</c:f>
+              <c:f>スマホ!$D$22:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>60</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>56</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>56</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>模試の記録!E1</c:f>
+              <c:f>"理科"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1167,34 +1237,31 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>模試の記録!$A$2:$A$10</c:f>
+              <c:f>スマホ!$A$22:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>志望の目安</c:v>
+                  <c:v>1回目</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1回目</c:v>
+                  <c:v>2回目</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2回目</c:v>
+                  <c:v>3回目</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3回目</c:v>
+                  <c:v>4回目</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4回目</c:v>
+                  <c:v>5回目</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5回目</c:v>
+                  <c:v>6回目</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6回目</c:v>
+                  <c:v>7回目</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7回目</c:v>
-                </c:pt>
-                <c:pt idx="8">
                   <c:v>8回目</c:v>
                 </c:pt>
               </c:strCache>
@@ -1202,30 +1269,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>模試の記録!$E$2:$E$10</c:f>
+              <c:f>スマホ!$E$22:$E$29</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>60</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>52</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>54</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>模試の記録!F1</c:f>
+              <c:f>"社会"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1275,34 +1339,31 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>模試の記録!$A$2:$A$10</c:f>
+              <c:f>スマホ!$A$22:$A$29</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>志望の目安</c:v>
+                  <c:v>1回目</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1回目</c:v>
+                  <c:v>2回目</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2回目</c:v>
+                  <c:v>3回目</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3回目</c:v>
+                  <c:v>4回目</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4回目</c:v>
+                  <c:v>5回目</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5回目</c:v>
+                  <c:v>6回目</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6回目</c:v>
+                  <c:v>7回目</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7回目</c:v>
-                </c:pt>
-                <c:pt idx="8">
                   <c:v>8回目</c:v>
                 </c:pt>
               </c:strCache>
@@ -1310,23 +1371,20 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>模試の記録!$F$2:$F$10</c:f>
+              <c:f>スマホ!$F$22:$F$29</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>60</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="2">
                   <c:v>55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
         </c:ser>
         <c:hiLowLines>
           <c:spPr>
@@ -1336,11 +1394,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="46626334"/>
-        <c:axId val="66873715"/>
+        <c:axId val="75682460"/>
+        <c:axId val="85363672"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="46626334"/>
+        <c:axId val="75682460"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1372,7 +1430,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66873715"/>
+        <c:crossAx val="85363672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1380,7 +1438,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66873715"/>
+        <c:axId val="85363672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1422,7 +1480,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46626334"/>
+        <c:crossAx val="75682460"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1434,7 +1492,707 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>教科別の推移</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"英語"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>英語</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>スマホ!$A$22:$A$29</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1回目</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2回目</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3回目</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4回目</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5回目</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6回目</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7回目</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8回目</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>スマホ!$B$22:$B$29</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>59</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"数学"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>数学</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>スマホ!$A$22:$A$29</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1回目</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2回目</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3回目</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4回目</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5回目</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6回目</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7回目</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8回目</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>スマホ!$C$22:$C$29</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"国語"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>国語</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>スマホ!$A$22:$A$29</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1回目</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2回目</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3回目</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4回目</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5回目</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6回目</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7回目</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8回目</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>スマホ!$D$22:$D$29</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"理科"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>理科</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7d5fa0"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="7d5fa0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>スマホ!$A$22:$A$29</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1回目</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2回目</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3回目</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4回目</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5回目</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6回目</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7回目</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8回目</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>スマホ!$E$22:$E$29</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>54</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"社会"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>社会</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="46aac4"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="46aac4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>スマホ!$A$22:$A$29</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1回目</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2回目</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3回目</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4回目</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5回目</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6回目</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7回目</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8回目</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>スマホ!$F$22:$F$29</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>55</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="74037806"/>
+        <c:axId val="40502674"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="74037806"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="40502674"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="40502674"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="74037806"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1480,6 +2238,41 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>161280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>352080</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>95400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="9391680"/>
+        <a:ext cx="3419640" cy="2519640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>159840</xdr:rowOff>
     </xdr:from>
@@ -1491,7 +2284,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvPr id="1" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1689,6 +2482,465 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="6.51"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="str">
+        <f aca="false">IF(ボード!B6="","",ボード!B6&amp;"（目安"&amp;ボード!C6&amp;"・差"&amp;TEXT(ボード!D6,"+0;-0;0")&amp;"）")</f>
+        <v>59（目安60・差-1）</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="str">
+        <f aca="false">IF(ボード!B7="","",ボード!B7&amp;"（目安"&amp;ボード!C7&amp;"・差"&amp;TEXT(ボード!D7,"+0;-0;0")&amp;"）")</f>
+        <v>52（目安60・差-8）</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="str">
+        <f aca="false">IF(ボード!B8="","",ボード!B8&amp;"（目安"&amp;ボード!C8&amp;"・差"&amp;TEXT(ボード!D8,"+0;-0;0")&amp;"）")</f>
+        <v>56（目安60・差-4）</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="str">
+        <f aca="false">IF(ボード!B9="","",ボード!B9&amp;"（目安"&amp;ボード!C9&amp;"・差"&amp;TEXT(ボード!D9,"+0;-0;0")&amp;"）")</f>
+        <v>54（目安60・差-6）</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="str">
+        <f aca="false">IF(ボード!B10="","",ボード!B10&amp;"（目安"&amp;ボード!C10&amp;"・差"&amp;TEXT(ボード!D10,"+0;-0;0")&amp;"）")</f>
+        <v>55（目安60・差-5）</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="5" t="str">
+        <f aca="false">IF(ボード!G6="","",ボード!G6&amp;"　"&amp;ボード!H6)</f>
+        <v>59　予測データ不足（3回以上で表示）</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5" t="str">
+        <f aca="false">IF(ボード!G7="","",ボード!G7&amp;"　"&amp;ボード!H7)</f>
+        <v>53　予測データ不足（3回以上で表示）</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="5" t="str">
+        <f aca="false">IF(ボード!G8="","",ボード!G8&amp;"　"&amp;ボード!H8)</f>
+        <v>57　予測データ不足（3回以上で表示）</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="5" t="str">
+        <f aca="false">IF(ボード!G9="","",ボード!G9&amp;"　"&amp;ボード!H9)</f>
+        <v>55　予測データ不足（3回以上で表示）</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="5" t="str">
+        <f aca="false">IF(ボード!G10="","",ボード!G10&amp;"　"&amp;ボード!H10)</f>
+        <v>56　予測データ不足（3回以上で表示）</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="17" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+    </row>
+    <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+    </row>
+    <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+    </row>
+    <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+    </row>
+    <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+    </row>
+    <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+    </row>
+    <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B17 B21:F29 B34:B39" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1696,53 +2948,53 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="12" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
+      <c r="A3" s="13" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
+      <c r="A4" s="13" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
+      <c r="A5" s="13" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>4</v>
+      <c r="A7" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>5</v>
+      <c r="A8" s="14" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>6</v>
+      <c r="A9" s="15" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>7</v>
+      <c r="A10" s="13" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>8</v>
+      <c r="A11" s="13" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>9</v>
+      <c r="A13" s="13" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1756,7 +3008,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1769,180 +3021,300 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>16</v>
+      <c r="B1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="17" t="n">
+        <f aca="false">IF(スマホ!B21="","",スマホ!B21)</f>
         <v>60</v>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="17" t="n">
+        <f aca="false">IF(スマホ!C21="","",スマホ!C21)</f>
         <v>60</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="17" t="n">
+        <f aca="false">IF(スマホ!D21="","",スマホ!D21)</f>
         <v>60</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="17" t="n">
+        <f aca="false">IF(スマホ!E21="","",スマホ!E21)</f>
         <v>60</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" s="17" t="n">
+        <f aca="false">IF(スマホ!F21="","",スマホ!F21)</f>
         <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="17" t="n">
+        <f aca="false">IF(スマホ!B22="","",スマホ!B22)</f>
         <v>58</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="17" t="n">
+        <f aca="false">IF(スマホ!C22="","",スマホ!C22)</f>
         <v>49</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="17" t="n">
+        <f aca="false">IF(スマホ!D22="","",スマホ!D22)</f>
         <v>56</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="17" t="n">
+        <f aca="false">IF(スマホ!E22="","",スマホ!E22)</f>
         <v>52</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="17" t="n">
+        <f aca="false">IF(スマホ!F22="","",スマホ!F22)</f>
         <v>55</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="16" t="str">
+        <f aca="false">IF(スマホ!B32="","",スマホ!B32)</f>
+        <v>（例）◯◯模試</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="B4" s="17" t="n">
+        <f aca="false">IF(スマホ!B23="","",スマホ!B23)</f>
+        <v>59</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <f aca="false">IF(スマホ!C23="","",スマホ!C23)</f>
+        <v>52</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <f aca="false">IF(スマホ!D23="","",スマホ!D23)</f>
+        <v>56</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <f aca="false">IF(スマホ!E23="","",スマホ!E23)</f>
+        <v>54</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <f aca="false">IF(スマホ!F23="","",スマホ!F23)</f>
+        <v>55</v>
+      </c>
+      <c r="G4" s="16" t="str">
+        <f aca="false">IF(スマホ!B33="","",スマホ!B33)</f>
+        <v>（例）◯◯模試</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="C4" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+      <c r="B5" s="17" t="str">
+        <f aca="false">IF(スマホ!B24="","",スマホ!B24)</f>
+        <v/>
+      </c>
+      <c r="C5" s="17" t="str">
+        <f aca="false">IF(スマホ!C24="","",スマホ!C24)</f>
+        <v/>
+      </c>
+      <c r="D5" s="17" t="str">
+        <f aca="false">IF(スマホ!D24="","",スマホ!D24)</f>
+        <v/>
+      </c>
+      <c r="E5" s="17" t="str">
+        <f aca="false">IF(スマホ!E24="","",スマホ!E24)</f>
+        <v/>
+      </c>
+      <c r="F5" s="17" t="str">
+        <f aca="false">IF(スマホ!F24="","",スマホ!F24)</f>
+        <v/>
+      </c>
+      <c r="G5" s="16" t="str">
+        <f aca="false">IF(スマホ!B34="","",スマホ!B34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="B6" s="17" t="str">
+        <f aca="false">IF(スマホ!B25="","",スマホ!B25)</f>
+        <v/>
+      </c>
+      <c r="C6" s="17" t="str">
+        <f aca="false">IF(スマホ!C25="","",スマホ!C25)</f>
+        <v/>
+      </c>
+      <c r="D6" s="17" t="str">
+        <f aca="false">IF(スマホ!D25="","",スマホ!D25)</f>
+        <v/>
+      </c>
+      <c r="E6" s="17" t="str">
+        <f aca="false">IF(スマホ!E25="","",スマホ!E25)</f>
+        <v/>
+      </c>
+      <c r="F6" s="17" t="str">
+        <f aca="false">IF(スマホ!F25="","",スマホ!F25)</f>
+        <v/>
+      </c>
+      <c r="G6" s="16" t="str">
+        <f aca="false">IF(スマホ!B35="","",スマホ!B35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="10"/>
-    </row>
-    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
+      <c r="B7" s="17" t="str">
+        <f aca="false">IF(スマホ!B26="","",スマホ!B26)</f>
+        <v/>
+      </c>
+      <c r="C7" s="17" t="str">
+        <f aca="false">IF(スマホ!C26="","",スマホ!C26)</f>
+        <v/>
+      </c>
+      <c r="D7" s="17" t="str">
+        <f aca="false">IF(スマホ!D26="","",スマホ!D26)</f>
+        <v/>
+      </c>
+      <c r="E7" s="17" t="str">
+        <f aca="false">IF(スマホ!E26="","",スマホ!E26)</f>
+        <v/>
+      </c>
+      <c r="F7" s="17" t="str">
+        <f aca="false">IF(スマホ!F26="","",スマホ!F26)</f>
+        <v/>
+      </c>
+      <c r="G7" s="16" t="str">
+        <f aca="false">IF(スマホ!B36="","",スマホ!B36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+      <c r="B8" s="17" t="str">
+        <f aca="false">IF(スマホ!B27="","",スマホ!B27)</f>
+        <v/>
+      </c>
+      <c r="C8" s="17" t="str">
+        <f aca="false">IF(スマホ!C27="","",スマホ!C27)</f>
+        <v/>
+      </c>
+      <c r="D8" s="17" t="str">
+        <f aca="false">IF(スマホ!D27="","",スマホ!D27)</f>
+        <v/>
+      </c>
+      <c r="E8" s="17" t="str">
+        <f aca="false">IF(スマホ!E27="","",スマホ!E27)</f>
+        <v/>
+      </c>
+      <c r="F8" s="17" t="str">
+        <f aca="false">IF(スマホ!F27="","",スマホ!F27)</f>
+        <v/>
+      </c>
+      <c r="G8" s="16" t="str">
+        <f aca="false">IF(スマホ!B37="","",スマホ!B37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="B9" s="17" t="str">
+        <f aca="false">IF(スマホ!B28="","",スマホ!B28)</f>
+        <v/>
+      </c>
+      <c r="C9" s="17" t="str">
+        <f aca="false">IF(スマホ!C28="","",スマホ!C28)</f>
+        <v/>
+      </c>
+      <c r="D9" s="17" t="str">
+        <f aca="false">IF(スマホ!D28="","",スマホ!D28)</f>
+        <v/>
+      </c>
+      <c r="E9" s="17" t="str">
+        <f aca="false">IF(スマホ!E28="","",スマホ!E28)</f>
+        <v/>
+      </c>
+      <c r="F9" s="17" t="str">
+        <f aca="false">IF(スマホ!F28="","",スマホ!F28)</f>
+        <v/>
+      </c>
+      <c r="G9" s="16" t="str">
+        <f aca="false">IF(スマホ!B38="","",スマホ!B38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="10"/>
+      <c r="B10" s="17" t="str">
+        <f aca="false">IF(スマホ!B29="","",スマホ!B29)</f>
+        <v/>
+      </c>
+      <c r="C10" s="17" t="str">
+        <f aca="false">IF(スマホ!C29="","",スマホ!C29)</f>
+        <v/>
+      </c>
+      <c r="D10" s="17" t="str">
+        <f aca="false">IF(スマホ!D29="","",スマホ!D29)</f>
+        <v/>
+      </c>
+      <c r="E10" s="17" t="str">
+        <f aca="false">IF(スマホ!E29="","",スマホ!E29)</f>
+        <v/>
+      </c>
+      <c r="F10" s="17" t="str">
+        <f aca="false">IF(スマホ!F29="","",スマホ!F29)</f>
+        <v/>
+      </c>
+      <c r="G10" s="16" t="str">
+        <f aca="false">IF(スマホ!B39="","",スマホ!B39)</f>
+        <v/>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="8" t="n">
+      <c r="A12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">スマホ!B17</f>
         <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>28</v>
+      <c r="A13" s="13" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:F10 G5:G10 B12" type="decimal">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1953,7 +3325,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1971,227 +3343,227 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>29</v>
+      <c r="A1" s="12" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="12" t="n">
+      <c r="A2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="17" t="n">
         <f aca="false">MAX(COUNT(模試の記録!B3:B10),COUNT(模試の記録!C3:C10),COUNT(模試の記録!D3:D10),COUNT(模試の記録!E3:E10),COUNT(模試の記録!F3:F10))</f>
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="12" t="n">
+      <c r="A3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="17" t="n">
         <f aca="false">MAX(模試の記録!B12-B2,0)</f>
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="A5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>38</v>
+      <c r="D5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="14" t="n">
+      <c r="A6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!B3:B10&lt;&gt;""),模試の記録!B3:B10),"")</f>
         <v>59</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="17" t="n">
         <f aca="false">模試の記録!B2</f>
         <v>60</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="21" t="n">
         <f aca="false">IFERROR(B6-C6,"")</f>
         <v>-1</v>
       </c>
-      <c r="E6" s="16" t="str">
+      <c r="E6" s="22" t="str">
         <f aca="false">IFERROR(IF(COUNT(模試の記録!B3:B10)&lt;3,"",(B6-模試の記録!B3)/(COUNT(模試の記録!B3:B10)-1)),"")</f>
         <v/>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="23" t="n">
         <f aca="false">IFERROR(IF(D6&gt;=0,0,IF($B$3=0,"",-D6/$B$3)),"")</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="20" t="n">
         <f aca="false">IFERROR(IF(D6&gt;=0,B6,ROUND(B6+F6,0)),"")</f>
         <v>59</v>
       </c>
-      <c r="H6" s="18" t="str">
+      <c r="H6" s="24" t="str">
         <f aca="false">IFERROR(IF(B6="","",IF(D6&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E6="","予測データ不足（3回以上で表示）",IF(E6&gt;=F6,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
         <v>予測データ不足（3回以上で表示）</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="14" t="n">
+      <c r="A7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!C3:C10&lt;&gt;""),模試の記録!C3:C10),"")</f>
         <v>52</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="17" t="n">
         <f aca="false">模試の記録!C2</f>
         <v>60</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="21" t="n">
         <f aca="false">IFERROR(B7-C7,"")</f>
         <v>-8</v>
       </c>
-      <c r="E7" s="16" t="str">
+      <c r="E7" s="22" t="str">
         <f aca="false">IFERROR(IF(COUNT(模試の記録!C3:C10)&lt;3,"",(B7-模試の記録!C3)/(COUNT(模試の記録!C3:C10)-1)),"")</f>
         <v/>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="23" t="n">
         <f aca="false">IFERROR(IF(D7&gt;=0,0,IF($B$3=0,"",-D7/$B$3)),"")</f>
         <v>1.33333333333333</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="20" t="n">
         <f aca="false">IFERROR(IF(D7&gt;=0,B7,ROUND(B7+F7,0)),"")</f>
         <v>53</v>
       </c>
-      <c r="H7" s="18" t="str">
+      <c r="H7" s="24" t="str">
         <f aca="false">IFERROR(IF(B7="","",IF(D7&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E7="","予測データ不足（3回以上で表示）",IF(E7&gt;=F7,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
         <v>予測データ不足（3回以上で表示）</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="14" t="n">
+      <c r="A8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!D3:D10&lt;&gt;""),模試の記録!D3:D10),"")</f>
         <v>56</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="17" t="n">
         <f aca="false">模試の記録!D2</f>
         <v>60</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="21" t="n">
         <f aca="false">IFERROR(B8-C8,"")</f>
         <v>-4</v>
       </c>
-      <c r="E8" s="16" t="str">
+      <c r="E8" s="22" t="str">
         <f aca="false">IFERROR(IF(COUNT(模試の記録!D3:D10)&lt;3,"",(B8-模試の記録!D3)/(COUNT(模試の記録!D3:D10)-1)),"")</f>
         <v/>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="23" t="n">
         <f aca="false">IFERROR(IF(D8&gt;=0,0,IF($B$3=0,"",-D8/$B$3)),"")</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="20" t="n">
         <f aca="false">IFERROR(IF(D8&gt;=0,B8,ROUND(B8+F8,0)),"")</f>
         <v>57</v>
       </c>
-      <c r="H8" s="18" t="str">
+      <c r="H8" s="24" t="str">
         <f aca="false">IFERROR(IF(B8="","",IF(D8&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E8="","予測データ不足（3回以上で表示）",IF(E8&gt;=F8,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
         <v>予測データ不足（3回以上で表示）</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="14" t="n">
+      <c r="A9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!E3:E10&lt;&gt;""),模試の記録!E3:E10),"")</f>
         <v>54</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="17" t="n">
         <f aca="false">模試の記録!E2</f>
         <v>60</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="21" t="n">
         <f aca="false">IFERROR(B9-C9,"")</f>
         <v>-6</v>
       </c>
-      <c r="E9" s="16" t="str">
+      <c r="E9" s="22" t="str">
         <f aca="false">IFERROR(IF(COUNT(模試の記録!E3:E10)&lt;3,"",(B9-模試の記録!E3)/(COUNT(模試の記録!E3:E10)-1)),"")</f>
         <v/>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="23" t="n">
         <f aca="false">IFERROR(IF(D9&gt;=0,0,IF($B$3=0,"",-D9/$B$3)),"")</f>
         <v>1</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="20" t="n">
         <f aca="false">IFERROR(IF(D9&gt;=0,B9,ROUND(B9+F9,0)),"")</f>
         <v>55</v>
       </c>
-      <c r="H9" s="18" t="str">
+      <c r="H9" s="24" t="str">
         <f aca="false">IFERROR(IF(B9="","",IF(D9&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E9="","予測データ不足（3回以上で表示）",IF(E9&gt;=F9,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
         <v>予測データ不足（3回以上で表示）</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="14" t="n">
+      <c r="A10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="20" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!F3:F10&lt;&gt;""),模試の記録!F3:F10),"")</f>
         <v>55</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="17" t="n">
         <f aca="false">模試の記録!F2</f>
         <v>60</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="21" t="n">
         <f aca="false">IFERROR(B10-C10,"")</f>
         <v>-5</v>
       </c>
-      <c r="E10" s="16" t="str">
+      <c r="E10" s="22" t="str">
         <f aca="false">IFERROR(IF(COUNT(模試の記録!F3:F10)&lt;3,"",(B10-模試の記録!F3)/(COUNT(模試の記録!F3:F10)-1)),"")</f>
         <v/>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="23" t="n">
         <f aca="false">IFERROR(IF(D10&gt;=0,0,IF($B$3=0,"",-D10/$B$3)),"")</f>
         <v>0.833333333333333</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="20" t="n">
         <f aca="false">IFERROR(IF(D10&gt;=0,B10,ROUND(B10+F10,0)),"")</f>
         <v>56</v>
       </c>
-      <c r="H10" s="18" t="str">
+      <c r="H10" s="24" t="str">
         <f aca="false">IFERROR(IF(B10="","",IF(D10&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E10="","予測データ不足（3回以上で表示）",IF(E10&gt;=F10,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
         <v>予測データ不足（3回以上で表示）</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>39</v>
+      <c r="A12" s="13" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>40</v>
+      <c r="A13" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/docs/platform/p1-kit/boards/board-04-exam.xlsx
+++ b/docs/platform/p1-kit/boards/board-04-exam.xlsx
@@ -1394,11 +1394,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="75682460"/>
-        <c:axId val="85363672"/>
+        <c:axId val="45659836"/>
+        <c:axId val="48983674"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="75682460"/>
+        <c:axId val="45659836"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1430,7 +1430,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85363672"/>
+        <c:crossAx val="48983674"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1438,7 +1438,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="85363672"/>
+        <c:axId val="48983674"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1480,7 +1480,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75682460"/>
+        <c:crossAx val="45659836"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2094,11 +2094,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="74037806"/>
-        <c:axId val="40502674"/>
+        <c:axId val="77625470"/>
+        <c:axId val="99032447"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="74037806"/>
+        <c:axId val="77625470"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2130,7 +2130,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40502674"/>
+        <c:crossAx val="99032447"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2138,7 +2138,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40502674"/>
+        <c:axId val="99032447"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2180,7 +2180,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74037806"/>
+        <c:crossAx val="77625470"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3396,7 +3396,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="20" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!B3:B10&lt;&gt;""),模試の記録!B3:B10),"")</f>
+        <f aca="false">IFERROR(INDEX(模試の記録!B3:B10,MATCH(9.99E+307,模試の記録!B3:B10)),"")</f>
         <v>59</v>
       </c>
       <c r="C6" s="17" t="n">
@@ -3429,7 +3429,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="20" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!C3:C10&lt;&gt;""),模試の記録!C3:C10),"")</f>
+        <f aca="false">IFERROR(INDEX(模試の記録!C3:C10,MATCH(9.99E+307,模試の記録!C3:C10)),"")</f>
         <v>52</v>
       </c>
       <c r="C7" s="17" t="n">
@@ -3462,7 +3462,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="20" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!D3:D10&lt;&gt;""),模試の記録!D3:D10),"")</f>
+        <f aca="false">IFERROR(INDEX(模試の記録!D3:D10,MATCH(9.99E+307,模試の記録!D3:D10)),"")</f>
         <v>56</v>
       </c>
       <c r="C8" s="17" t="n">
@@ -3495,7 +3495,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="20" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!E3:E10&lt;&gt;""),模試の記録!E3:E10),"")</f>
+        <f aca="false">IFERROR(INDEX(模試の記録!E3:E10,MATCH(9.99E+307,模試の記録!E3:E10)),"")</f>
         <v>54</v>
       </c>
       <c r="C9" s="17" t="n">
@@ -3528,7 +3528,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="20" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(模試の記録!F3:F10&lt;&gt;""),模試の記録!F3:F10),"")</f>
+        <f aca="false">IFERROR(INDEX(模試の記録!F3:F10,MATCH(9.99E+307,模試の記録!F3:F10)),"")</f>
         <v>55</v>
       </c>
       <c r="C10" s="17" t="n">

--- a/docs/platform/p1-kit/boards/board-04-exam.xlsx
+++ b/docs/platform/p1-kit/boards/board-04-exam.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="55">
   <si>
     <t xml:space="preserve">④ スマホで見る：受験</t>
   </si>
@@ -52,7 +52,7 @@
     <t xml:space="preserve">見込みと目標は過去の数値を直線で延ばした参考計算で、合格の可能性の予測ではありません。できるだけ同じ会社・同じシリーズの模試で比べてください。</t>
   </si>
   <si>
-    <t xml:space="preserve">受験までの模試の回数（全部）</t>
+    <t xml:space="preserve">受験までに受ける模試の回数（全部）→</t>
   </si>
   <si>
     <t xml:space="preserve">■ 数字を入れる（模試ごと・偏差値または点数）</t>
@@ -76,7 +76,7 @@
     <t xml:space="preserve">社</t>
   </si>
   <si>
-    <t xml:space="preserve">志望の目安</t>
+    <t xml:space="preserve">目安</t>
   </si>
   <si>
     <r>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t xml:space="preserve">模試の名前（会社・シリーズ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">志望の目安</t>
   </si>
   <si>
     <t xml:space="preserve">受験までに受ける模試の回数（全部で）</t>
@@ -659,7 +662,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -668,7 +671,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -686,6 +689,10 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -713,6 +720,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1394,11 +1405,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="45659836"/>
-        <c:axId val="48983674"/>
+        <c:axId val="4698261"/>
+        <c:axId val="12084256"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="45659836"/>
+        <c:axId val="4698261"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1430,7 +1441,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48983674"/>
+        <c:crossAx val="12084256"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1438,7 +1449,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48983674"/>
+        <c:axId val="12084256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1480,7 +1491,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45659836"/>
+        <c:crossAx val="4698261"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2094,11 +2105,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="77625470"/>
-        <c:axId val="99032447"/>
+        <c:axId val="72440738"/>
+        <c:axId val="22887232"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="77625470"/>
+        <c:axId val="72440738"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2130,7 +2141,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99032447"/>
+        <c:crossAx val="22887232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2138,7 +2149,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99032447"/>
+        <c:axId val="22887232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2180,7 +2191,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77625470"/>
+        <c:crossAx val="72440738"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2238,14 +2249,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>161280</xdr:rowOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>151200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>352080</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>95400</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>139680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2503,6 +2514,11 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
@@ -2573,6 +2589,11 @@
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
@@ -2649,11 +2670,14 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="17" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="8" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2661,44 +2685,49 @@
       <c r="A19" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="8" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2706,19 +2735,19 @@
       <c r="A22" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B22" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="8" t="n">
         <v>55</v>
       </c>
     </row>
@@ -2726,19 +2755,19 @@
       <c r="A23" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="E23" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="8" t="n">
         <v>55</v>
       </c>
     </row>
@@ -2746,170 +2775,185 @@
       <c r="A24" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="26">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B34:F34"/>
@@ -2918,9 +2962,10 @@
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="A41:F41"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B17 B21:F29 B34:B39" type="decimal">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E17 B21:F29 B34:B39" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2948,52 +2993,52 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="16" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="17" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="14" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3021,297 +3066,297 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="17" t="n">
+      <c r="A2" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="19" t="n">
         <f aca="false">IF(スマホ!B21="","",スマホ!B21)</f>
         <v>60</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="19" t="n">
         <f aca="false">IF(スマホ!C21="","",スマホ!C21)</f>
         <v>60</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="19" t="n">
         <f aca="false">IF(スマホ!D21="","",スマホ!D21)</f>
         <v>60</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="19" t="n">
         <f aca="false">IF(スマホ!E21="","",スマホ!E21)</f>
         <v>60</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="19" t="n">
         <f aca="false">IF(スマホ!F21="","",スマホ!F21)</f>
         <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="19" t="n">
         <f aca="false">IF(スマホ!B22="","",スマホ!B22)</f>
         <v>58</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="19" t="n">
         <f aca="false">IF(スマホ!C22="","",スマホ!C22)</f>
         <v>49</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="19" t="n">
         <f aca="false">IF(スマホ!D22="","",スマホ!D22)</f>
         <v>56</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="19" t="n">
         <f aca="false">IF(スマホ!E22="","",スマホ!E22)</f>
         <v>52</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="19" t="n">
         <f aca="false">IF(スマホ!F22="","",スマホ!F22)</f>
         <v>55</v>
       </c>
-      <c r="G3" s="16" t="str">
+      <c r="G3" s="18" t="str">
         <f aca="false">IF(スマホ!B32="","",スマホ!B32)</f>
         <v>（例）◯◯模試</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="19" t="n">
         <f aca="false">IF(スマホ!B23="","",スマホ!B23)</f>
         <v>59</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="19" t="n">
         <f aca="false">IF(スマホ!C23="","",スマホ!C23)</f>
         <v>52</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="19" t="n">
         <f aca="false">IF(スマホ!D23="","",スマホ!D23)</f>
         <v>56</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="19" t="n">
         <f aca="false">IF(スマホ!E23="","",スマホ!E23)</f>
         <v>54</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="19" t="n">
         <f aca="false">IF(スマホ!F23="","",スマホ!F23)</f>
         <v>55</v>
       </c>
-      <c r="G4" s="16" t="str">
+      <c r="G4" s="18" t="str">
         <f aca="false">IF(スマホ!B33="","",スマホ!B33)</f>
         <v>（例）◯◯模試</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="17" t="str">
+      <c r="B5" s="19" t="str">
         <f aca="false">IF(スマホ!B24="","",スマホ!B24)</f>
         <v/>
       </c>
-      <c r="C5" s="17" t="str">
+      <c r="C5" s="19" t="str">
         <f aca="false">IF(スマホ!C24="","",スマホ!C24)</f>
         <v/>
       </c>
-      <c r="D5" s="17" t="str">
+      <c r="D5" s="19" t="str">
         <f aca="false">IF(スマホ!D24="","",スマホ!D24)</f>
         <v/>
       </c>
-      <c r="E5" s="17" t="str">
+      <c r="E5" s="19" t="str">
         <f aca="false">IF(スマホ!E24="","",スマホ!E24)</f>
         <v/>
       </c>
-      <c r="F5" s="17" t="str">
+      <c r="F5" s="19" t="str">
         <f aca="false">IF(スマホ!F24="","",スマホ!F24)</f>
         <v/>
       </c>
-      <c r="G5" s="16" t="str">
+      <c r="G5" s="18" t="str">
         <f aca="false">IF(スマホ!B34="","",スマホ!B34)</f>
         <v/>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="17" t="str">
+      <c r="B6" s="19" t="str">
         <f aca="false">IF(スマホ!B25="","",スマホ!B25)</f>
         <v/>
       </c>
-      <c r="C6" s="17" t="str">
+      <c r="C6" s="19" t="str">
         <f aca="false">IF(スマホ!C25="","",スマホ!C25)</f>
         <v/>
       </c>
-      <c r="D6" s="17" t="str">
+      <c r="D6" s="19" t="str">
         <f aca="false">IF(スマホ!D25="","",スマホ!D25)</f>
         <v/>
       </c>
-      <c r="E6" s="17" t="str">
+      <c r="E6" s="19" t="str">
         <f aca="false">IF(スマホ!E25="","",スマホ!E25)</f>
         <v/>
       </c>
-      <c r="F6" s="17" t="str">
+      <c r="F6" s="19" t="str">
         <f aca="false">IF(スマホ!F25="","",スマホ!F25)</f>
         <v/>
       </c>
-      <c r="G6" s="16" t="str">
+      <c r="G6" s="18" t="str">
         <f aca="false">IF(スマホ!B35="","",スマホ!B35)</f>
         <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="17" t="str">
+      <c r="B7" s="19" t="str">
         <f aca="false">IF(スマホ!B26="","",スマホ!B26)</f>
         <v/>
       </c>
-      <c r="C7" s="17" t="str">
+      <c r="C7" s="19" t="str">
         <f aca="false">IF(スマホ!C26="","",スマホ!C26)</f>
         <v/>
       </c>
-      <c r="D7" s="17" t="str">
+      <c r="D7" s="19" t="str">
         <f aca="false">IF(スマホ!D26="","",スマホ!D26)</f>
         <v/>
       </c>
-      <c r="E7" s="17" t="str">
+      <c r="E7" s="19" t="str">
         <f aca="false">IF(スマホ!E26="","",スマホ!E26)</f>
         <v/>
       </c>
-      <c r="F7" s="17" t="str">
+      <c r="F7" s="19" t="str">
         <f aca="false">IF(スマホ!F26="","",スマホ!F26)</f>
         <v/>
       </c>
-      <c r="G7" s="16" t="str">
+      <c r="G7" s="18" t="str">
         <f aca="false">IF(スマホ!B36="","",スマホ!B36)</f>
         <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="17" t="str">
+      <c r="B8" s="19" t="str">
         <f aca="false">IF(スマホ!B27="","",スマホ!B27)</f>
         <v/>
       </c>
-      <c r="C8" s="17" t="str">
+      <c r="C8" s="19" t="str">
         <f aca="false">IF(スマホ!C27="","",スマホ!C27)</f>
         <v/>
       </c>
-      <c r="D8" s="17" t="str">
+      <c r="D8" s="19" t="str">
         <f aca="false">IF(スマホ!D27="","",スマホ!D27)</f>
         <v/>
       </c>
-      <c r="E8" s="17" t="str">
+      <c r="E8" s="19" t="str">
         <f aca="false">IF(スマホ!E27="","",スマホ!E27)</f>
         <v/>
       </c>
-      <c r="F8" s="17" t="str">
+      <c r="F8" s="19" t="str">
         <f aca="false">IF(スマホ!F27="","",スマホ!F27)</f>
         <v/>
       </c>
-      <c r="G8" s="16" t="str">
+      <c r="G8" s="18" t="str">
         <f aca="false">IF(スマホ!B37="","",スマホ!B37)</f>
         <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="17" t="str">
+      <c r="B9" s="19" t="str">
         <f aca="false">IF(スマホ!B28="","",スマホ!B28)</f>
         <v/>
       </c>
-      <c r="C9" s="17" t="str">
+      <c r="C9" s="19" t="str">
         <f aca="false">IF(スマホ!C28="","",スマホ!C28)</f>
         <v/>
       </c>
-      <c r="D9" s="17" t="str">
+      <c r="D9" s="19" t="str">
         <f aca="false">IF(スマホ!D28="","",スマホ!D28)</f>
         <v/>
       </c>
-      <c r="E9" s="17" t="str">
+      <c r="E9" s="19" t="str">
         <f aca="false">IF(スマホ!E28="","",スマホ!E28)</f>
         <v/>
       </c>
-      <c r="F9" s="17" t="str">
+      <c r="F9" s="19" t="str">
         <f aca="false">IF(スマホ!F28="","",スマホ!F28)</f>
         <v/>
       </c>
-      <c r="G9" s="16" t="str">
+      <c r="G9" s="18" t="str">
         <f aca="false">IF(スマホ!B38="","",スマホ!B38)</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="17" t="str">
+      <c r="B10" s="19" t="str">
         <f aca="false">IF(スマホ!B29="","",スマホ!B29)</f>
         <v/>
       </c>
-      <c r="C10" s="17" t="str">
+      <c r="C10" s="19" t="str">
         <f aca="false">IF(スマホ!C29="","",スマホ!C29)</f>
         <v/>
       </c>
-      <c r="D10" s="17" t="str">
+      <c r="D10" s="19" t="str">
         <f aca="false">IF(スマホ!D29="","",スマホ!D29)</f>
         <v/>
       </c>
-      <c r="E10" s="17" t="str">
+      <c r="E10" s="19" t="str">
         <f aca="false">IF(スマホ!E29="","",スマホ!E29)</f>
         <v/>
       </c>
-      <c r="F10" s="17" t="str">
+      <c r="F10" s="19" t="str">
         <f aca="false">IF(スマホ!F29="","",スマホ!F29)</f>
         <v/>
       </c>
-      <c r="G10" s="16" t="str">
+      <c r="G10" s="18" t="str">
         <f aca="false">IF(スマホ!B39="","",スマホ!B39)</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="17" t="n">
-        <f aca="false">スマホ!B17</f>
+        <v>41</v>
+      </c>
+      <c r="B12" s="19" t="n">
+        <f aca="false">スマホ!E17</f>
         <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>41</v>
+      <c r="A13" s="14" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -3343,83 +3388,83 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
-        <v>42</v>
+      <c r="A1" s="13" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="B2" s="19" t="n">
         <f aca="false">MAX(COUNT(模試の記録!B3:B10),COUNT(模試の記録!C3:C10),COUNT(模試の記録!D3:D10),COUNT(模試の記録!E3:E10),COUNT(模試の記録!F3:F10))</f>
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="B3" s="19" t="n">
         <f aca="false">MAX(模試の記録!B12-B2,0)</f>
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="C5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="E5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>51</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(INDEX(模試の記録!B3:B10,MATCH(9.99E+307,模試の記録!B3:B10)),"")</f>
         <v>59</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="19" t="n">
         <f aca="false">模試の記録!B2</f>
         <v>60</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="23" t="n">
         <f aca="false">IFERROR(B6-C6,"")</f>
         <v>-1</v>
       </c>
-      <c r="E6" s="22" t="str">
+      <c r="E6" s="24" t="str">
         <f aca="false">IFERROR(IF(COUNT(模試の記録!B3:B10)&lt;3,"",(B6-模試の記録!B3)/(COUNT(模試の記録!B3:B10)-1)),"")</f>
         <v/>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="25" t="n">
         <f aca="false">IFERROR(IF(D6&gt;=0,0,IF($B$3=0,"",-D6/$B$3)),"")</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="22" t="n">
         <f aca="false">IFERROR(IF(D6&gt;=0,B6,ROUND(B6+F6,0)),"")</f>
         <v>59</v>
       </c>
-      <c r="H6" s="24" t="str">
+      <c r="H6" s="26" t="str">
         <f aca="false">IFERROR(IF(B6="","",IF(D6&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E6="","予測データ不足（3回以上で表示）",IF(E6&gt;=F6,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
         <v>予測データ不足（3回以上で表示）</v>
       </c>
@@ -3428,31 +3473,31 @@
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="22" t="n">
         <f aca="false">IFERROR(INDEX(模試の記録!C3:C10,MATCH(9.99E+307,模試の記録!C3:C10)),"")</f>
         <v>52</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="19" t="n">
         <f aca="false">模試の記録!C2</f>
         <v>60</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="23" t="n">
         <f aca="false">IFERROR(B7-C7,"")</f>
         <v>-8</v>
       </c>
-      <c r="E7" s="22" t="str">
+      <c r="E7" s="24" t="str">
         <f aca="false">IFERROR(IF(COUNT(模試の記録!C3:C10)&lt;3,"",(B7-模試の記録!C3)/(COUNT(模試の記録!C3:C10)-1)),"")</f>
         <v/>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="25" t="n">
         <f aca="false">IFERROR(IF(D7&gt;=0,0,IF($B$3=0,"",-D7/$B$3)),"")</f>
         <v>1.33333333333333</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="22" t="n">
         <f aca="false">IFERROR(IF(D7&gt;=0,B7,ROUND(B7+F7,0)),"")</f>
         <v>53</v>
       </c>
-      <c r="H7" s="24" t="str">
+      <c r="H7" s="26" t="str">
         <f aca="false">IFERROR(IF(B7="","",IF(D7&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E7="","予測データ不足（3回以上で表示）",IF(E7&gt;=F7,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
         <v>予測データ不足（3回以上で表示）</v>
       </c>
@@ -3461,31 +3506,31 @@
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="22" t="n">
         <f aca="false">IFERROR(INDEX(模試の記録!D3:D10,MATCH(9.99E+307,模試の記録!D3:D10)),"")</f>
         <v>56</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="19" t="n">
         <f aca="false">模試の記録!D2</f>
         <v>60</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="23" t="n">
         <f aca="false">IFERROR(B8-C8,"")</f>
         <v>-4</v>
       </c>
-      <c r="E8" s="22" t="str">
+      <c r="E8" s="24" t="str">
         <f aca="false">IFERROR(IF(COUNT(模試の記録!D3:D10)&lt;3,"",(B8-模試の記録!D3)/(COUNT(模試の記録!D3:D10)-1)),"")</f>
         <v/>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="25" t="n">
         <f aca="false">IFERROR(IF(D8&gt;=0,0,IF($B$3=0,"",-D8/$B$3)),"")</f>
         <v>0.666666666666667</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="22" t="n">
         <f aca="false">IFERROR(IF(D8&gt;=0,B8,ROUND(B8+F8,0)),"")</f>
         <v>57</v>
       </c>
-      <c r="H8" s="24" t="str">
+      <c r="H8" s="26" t="str">
         <f aca="false">IFERROR(IF(B8="","",IF(D8&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E8="","予測データ不足（3回以上で表示）",IF(E8&gt;=F8,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
         <v>予測データ不足（3回以上で表示）</v>
       </c>
@@ -3494,31 +3539,31 @@
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="22" t="n">
         <f aca="false">IFERROR(INDEX(模試の記録!E3:E10,MATCH(9.99E+307,模試の記録!E3:E10)),"")</f>
         <v>54</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="19" t="n">
         <f aca="false">模試の記録!E2</f>
         <v>60</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="23" t="n">
         <f aca="false">IFERROR(B9-C9,"")</f>
         <v>-6</v>
       </c>
-      <c r="E9" s="22" t="str">
+      <c r="E9" s="24" t="str">
         <f aca="false">IFERROR(IF(COUNT(模試の記録!E3:E10)&lt;3,"",(B9-模試の記録!E3)/(COUNT(模試の記録!E3:E10)-1)),"")</f>
         <v/>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="25" t="n">
         <f aca="false">IFERROR(IF(D9&gt;=0,0,IF($B$3=0,"",-D9/$B$3)),"")</f>
         <v>1</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="22" t="n">
         <f aca="false">IFERROR(IF(D9&gt;=0,B9,ROUND(B9+F9,0)),"")</f>
         <v>55</v>
       </c>
-      <c r="H9" s="24" t="str">
+      <c r="H9" s="26" t="str">
         <f aca="false">IFERROR(IF(B9="","",IF(D9&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E9="","予測データ不足（3回以上で表示）",IF(E9&gt;=F9,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
         <v>予測データ不足（3回以上で表示）</v>
       </c>
@@ -3527,43 +3572,43 @@
       <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="22" t="n">
         <f aca="false">IFERROR(INDEX(模試の記録!F3:F10,MATCH(9.99E+307,模試の記録!F3:F10)),"")</f>
         <v>55</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="19" t="n">
         <f aca="false">模試の記録!F2</f>
         <v>60</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="23" t="n">
         <f aca="false">IFERROR(B10-C10,"")</f>
         <v>-5</v>
       </c>
-      <c r="E10" s="22" t="str">
+      <c r="E10" s="24" t="str">
         <f aca="false">IFERROR(IF(COUNT(模試の記録!F3:F10)&lt;3,"",(B10-模試の記録!F3)/(COUNT(模試の記録!F3:F10)-1)),"")</f>
         <v/>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="25" t="n">
         <f aca="false">IFERROR(IF(D10&gt;=0,0,IF($B$3=0,"",-D10/$B$3)),"")</f>
         <v>0.833333333333333</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="22" t="n">
         <f aca="false">IFERROR(IF(D10&gt;=0,B10,ROUND(B10+F10,0)),"")</f>
         <v>56</v>
       </c>
-      <c r="H10" s="24" t="str">
+      <c r="H10" s="26" t="str">
         <f aca="false">IFERROR(IF(B10="","",IF(D10&gt;=0,"目安に到達",IF($B$3=0,"残りの模試がありません",IF(E10="","予測データ不足（3回以上で表示）",IF(E10&gt;=F10,"このペースなら届く計算","このペースでは届かない計算（配分の見直し）"))))),"")</f>
         <v>予測データ不足（3回以上で表示）</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>52</v>
+      <c r="A12" s="14" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>53</v>
+      <c r="A13" s="14" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
